--- a/data/GPS/Metricas_GPS.xlsx
+++ b/data/GPS/Metricas_GPS.xlsx
@@ -1,13 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30330"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE13D8E-A29B-4B72-BF15-02A1275E8CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="_ib" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="_synced_data" sheetId="2" r:id="rId6"/>
+    <sheet name="_ib" sheetId="1" r:id="rId1"/>
+    <sheet name="_synced_data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -131,25 +140,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -160,38 +170,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -199,7 +214,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -389,22 +404,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -413,21 +431,22 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="6" max="7" width="22.25"/>
+    <col min="6" max="7" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,9 +493,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>46237.0</v>
+        <v>46237</v>
       </c>
       <c r="B2" s="1">
         <v>71.62</v>
@@ -488,42 +507,42 @@
         <v>19</v>
       </c>
       <c r="E2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>46237.0</v>
+        <v>46237</v>
       </c>
       <c r="B3" s="1">
         <v>71.62</v>
@@ -532,45 +551,45 @@
         <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1">
-        <v>4.406</v>
+        <v>4.4059999999999997</v>
       </c>
       <c r="F3" s="1">
-        <v>0.116</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="G3" s="1">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="H3" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="1">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="K3" s="1">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="L3" s="1">
-        <v>4.442</v>
+        <v>4.4420000000000002</v>
       </c>
       <c r="M3" s="1">
         <v>-5.665</v>
       </c>
       <c r="N3" s="1">
-        <v>25.286</v>
+        <v>25.286000000000001</v>
       </c>
       <c r="O3" s="1">
         <v>980.9</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>46237.0</v>
+        <v>46237</v>
       </c>
       <c r="B4" s="1">
         <v>71.62</v>
@@ -585,39 +604,39 @@
         <v>3.93</v>
       </c>
       <c r="F4" s="1">
-        <v>0.051</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="G4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="K4" s="1">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="L4" s="1">
-        <v>4.353</v>
+        <v>4.3529999999999998</v>
       </c>
       <c r="M4" s="1">
-        <v>-4.295</v>
+        <v>-4.2949999999999999</v>
       </c>
       <c r="N4" s="1">
-        <v>21.953</v>
+        <v>21.952999999999999</v>
       </c>
       <c r="O4" s="1">
         <v>636.6</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>46237.0</v>
+        <v>46237</v>
       </c>
       <c r="B5" s="1">
         <v>71.62</v>
@@ -629,42 +648,42 @@
         <v>24</v>
       </c>
       <c r="E5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O5" s="1">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>46237.0</v>
+        <v>46237</v>
       </c>
       <c r="B6" s="1">
         <v>71.62</v>
@@ -676,42 +695,42 @@
         <v>22</v>
       </c>
       <c r="E6" s="1">
-        <v>4.249</v>
+        <v>4.2489999999999997</v>
       </c>
       <c r="F6" s="1">
         <v>0.111</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="K6" s="1">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="L6" s="1">
-        <v>5.197</v>
+        <v>5.1970000000000001</v>
       </c>
       <c r="M6" s="1">
-        <v>-4.752</v>
+        <v>-4.7519999999999998</v>
       </c>
       <c r="N6" s="1">
-        <v>24.833</v>
+        <v>24.832999999999998</v>
       </c>
       <c r="O6" s="1">
         <v>955.3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46237.0</v>
+        <v>46237</v>
       </c>
       <c r="B7" s="1">
         <v>71.62</v>
@@ -726,28 +745,28 @@
         <v>3.976</v>
       </c>
       <c r="F7" s="1">
-        <v>0.024</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="K7" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="L7" s="1">
-        <v>4.962</v>
+        <v>4.9619999999999997</v>
       </c>
       <c r="M7" s="1">
-        <v>-4.597</v>
+        <v>-4.5970000000000004</v>
       </c>
       <c r="N7" s="1">
         <v>20.192</v>
@@ -756,9 +775,9 @@
         <v>954.2</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>46237.0</v>
+        <v>46237</v>
       </c>
       <c r="B8" s="1">
         <v>71.62</v>
@@ -770,28 +789,28 @@
         <v>27</v>
       </c>
       <c r="E8" s="1">
-        <v>3.796</v>
+        <v>3.7959999999999998</v>
       </c>
       <c r="F8" s="1">
-        <v>0.034</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="G8" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="K8" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="L8" s="1">
-        <v>4.025</v>
+        <v>4.0250000000000004</v>
       </c>
       <c r="M8" s="1">
         <v>-4.53</v>
@@ -803,9 +822,9 @@
         <v>903.4</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>46237.0</v>
+        <v>46237</v>
       </c>
       <c r="B9" s="1">
         <v>71.62</v>
@@ -817,42 +836,42 @@
         <v>30</v>
       </c>
       <c r="E9" s="1">
-        <v>4.089</v>
+        <v>4.0890000000000004</v>
       </c>
       <c r="F9" s="1">
-        <v>0.059</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="G9" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="K9" s="1">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="L9" s="1">
-        <v>4.354</v>
+        <v>4.3540000000000001</v>
       </c>
       <c r="M9" s="1">
-        <v>-5.354</v>
+        <v>-5.3540000000000001</v>
       </c>
       <c r="N9" s="1">
-        <v>22.806</v>
+        <v>22.806000000000001</v>
       </c>
       <c r="O9" s="1">
         <v>1045.5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>46237.0</v>
+        <v>46237</v>
       </c>
       <c r="B10" s="1">
         <v>71.62</v>
@@ -864,42 +883,42 @@
         <v>24</v>
       </c>
       <c r="E10" s="1">
-        <v>4.187</v>
+        <v>4.1870000000000003</v>
       </c>
       <c r="F10" s="1">
-        <v>0.043</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="G10" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I10" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="K10" s="1">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="L10" s="1">
-        <v>4.629</v>
+        <v>4.6289999999999996</v>
       </c>
       <c r="M10" s="1">
         <v>-4.931</v>
       </c>
       <c r="N10" s="1">
-        <v>24.196</v>
+        <v>24.196000000000002</v>
       </c>
       <c r="O10" s="1">
         <v>1287.2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>46237.0</v>
+        <v>46237</v>
       </c>
       <c r="B11" s="1">
         <v>71.62</v>
@@ -911,42 +930,42 @@
         <v>24</v>
       </c>
       <c r="E11" s="1">
-        <v>2.639</v>
+        <v>2.6389999999999998</v>
       </c>
       <c r="F11" s="1">
         <v>0.03</v>
       </c>
       <c r="G11" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="K11" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L11" s="1">
         <v>4.57</v>
       </c>
       <c r="M11" s="1">
-        <v>-3.691</v>
+        <v>-3.6909999999999998</v>
       </c>
       <c r="N11" s="1">
-        <v>20.862</v>
+        <v>20.861999999999998</v>
       </c>
       <c r="O11" s="1">
         <v>506.2</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>46237.0</v>
+        <v>46237</v>
       </c>
       <c r="B12" s="1">
         <v>71.62</v>
@@ -958,31 +977,31 @@
         <v>19</v>
       </c>
       <c r="E12" s="1">
-        <v>4.531</v>
+        <v>4.5309999999999997</v>
       </c>
       <c r="F12" s="1">
-        <v>0.078</v>
+        <v>7.8E-2</v>
       </c>
       <c r="G12" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="K12" s="1">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="L12" s="1">
         <v>4.62</v>
       </c>
       <c r="M12" s="1">
-        <v>-5.036</v>
+        <v>-5.0359999999999996</v>
       </c>
       <c r="N12" s="1">
         <v>23.53</v>
@@ -991,9 +1010,9 @@
         <v>1226.8</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>46237.0</v>
+        <v>46237</v>
       </c>
       <c r="B13" s="1">
         <v>71.62</v>
@@ -1005,28 +1024,28 @@
         <v>35</v>
       </c>
       <c r="E13" s="1">
-        <v>4.166</v>
+        <v>4.1660000000000004</v>
       </c>
       <c r="F13" s="1">
-        <v>0.084</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="G13" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I13" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="K13" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="L13" s="1">
-        <v>4.429</v>
+        <v>4.4290000000000003</v>
       </c>
       <c r="M13" s="1">
         <v>-4.726</v>
@@ -1038,9 +1057,9 @@
         <v>1102.2</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>46237.0</v>
+        <v>46237</v>
       </c>
       <c r="B14" s="1">
         <v>71.62</v>
@@ -1055,39 +1074,39 @@
         <v>3.919</v>
       </c>
       <c r="F14" s="1">
-        <v>0.073</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="G14" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I14" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="K14" s="1">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="L14" s="1">
-        <v>3.644</v>
+        <v>3.6440000000000001</v>
       </c>
       <c r="M14" s="1">
-        <v>-4.741</v>
+        <v>-4.7409999999999997</v>
       </c>
       <c r="N14" s="1">
-        <v>23.767</v>
+        <v>23.766999999999999</v>
       </c>
       <c r="O14" s="1">
         <v>825.1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>46237.0</v>
+        <v>46237</v>
       </c>
       <c r="B15" s="1">
         <v>71.62</v>
@@ -1102,28 +1121,28 @@
         <v>3.887</v>
       </c>
       <c r="F15" s="1">
-        <v>0.065</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="G15" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I15" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="K15" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="L15" s="1">
-        <v>4.232</v>
+        <v>4.2320000000000002</v>
       </c>
       <c r="M15" s="1">
-        <v>-5.784</v>
+        <v>-5.7839999999999998</v>
       </c>
       <c r="N15" s="1">
         <v>24.041</v>
@@ -1133,6 +1152,6 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/GPS/Metricas_GPS.xlsx
+++ b/data/GPS/Metricas_GPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE13D8E-A29B-4B72-BF15-02A1275E8CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878BA66B-4A40-40A1-9694-2B49FE7A4E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -444,6 +444,11 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="22.21875" customWidth="1"/>
+    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">

--- a/data/GPS/Metricas_GPS.xlsx
+++ b/data/GPS/Metricas_GPS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30405"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878BA66B-4A40-40A1-9694-2B49FE7A4E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE5929F-8C05-488E-8840-B54F7164F3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="_ib" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -77,9 +77,6 @@
     <t>Player Load</t>
   </si>
   <si>
-    <t xml:space="preserve">Daniel_Diaz_Alvaro </t>
-  </si>
-  <si>
     <t>Extremo</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
   </si>
   <si>
     <t>Mediapunta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carlos_De_La_Fe_Simon </t>
   </si>
   <si>
     <t>Mediocentro</t>
@@ -440,7 +434,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="22.21875" customWidth="1"/>
@@ -506,43 +500,43 @@
         <v>71.62</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1">
-        <v>0</v>
+        <v>4.4059999999999997</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L2" s="1">
-        <v>0</v>
+        <v>4.4420000000000002</v>
       </c>
       <c r="M2" s="1">
-        <v>0</v>
+        <v>-5.665</v>
       </c>
       <c r="N2" s="1">
-        <v>0</v>
+        <v>25.286000000000001</v>
       </c>
       <c r="O2" s="1">
-        <v>0</v>
+        <v>980.9</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -556,40 +550,40 @@
         <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1">
-        <v>4.4059999999999997</v>
+        <v>3.93</v>
       </c>
       <c r="F3" s="1">
-        <v>0.11600000000000001</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="G3" s="1">
-        <v>1E-3</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="K3" s="1">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="L3" s="1">
-        <v>4.4420000000000002</v>
+        <v>4.3529999999999998</v>
       </c>
       <c r="M3" s="1">
-        <v>-5.665</v>
+        <v>-4.2949999999999999</v>
       </c>
       <c r="N3" s="1">
-        <v>25.286000000000001</v>
+        <v>21.952999999999999</v>
       </c>
       <c r="O3" s="1">
-        <v>980.9</v>
+        <v>636.6</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -600,16 +594,16 @@
         <v>71.62</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="E4" s="1">
-        <v>3.93</v>
+        <v>4.2489999999999997</v>
       </c>
       <c r="F4" s="1">
-        <v>5.0999999999999997E-2</v>
+        <v>0.111</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -621,22 +615,22 @@
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="K4" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L4" s="1">
-        <v>4.3529999999999998</v>
+        <v>5.1970000000000001</v>
       </c>
       <c r="M4" s="1">
-        <v>-4.2949999999999999</v>
+        <v>-4.7519999999999998</v>
       </c>
       <c r="N4" s="1">
-        <v>21.952999999999999</v>
+        <v>24.832999999999998</v>
       </c>
       <c r="O4" s="1">
-        <v>636.6</v>
+        <v>955.3</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -647,16 +641,16 @@
         <v>71.62</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>3.976</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -668,22 +662,22 @@
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L5" s="1">
-        <v>0</v>
+        <v>4.9619999999999997</v>
       </c>
       <c r="M5" s="1">
-        <v>0</v>
+        <v>-4.5970000000000004</v>
       </c>
       <c r="N5" s="1">
-        <v>0</v>
+        <v>20.192</v>
       </c>
       <c r="O5" s="1">
-        <v>0</v>
+        <v>954.2</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -694,16 +688,16 @@
         <v>71.62</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="E6" s="1">
-        <v>4.2489999999999997</v>
+        <v>3.7959999999999998</v>
       </c>
       <c r="F6" s="1">
-        <v>0.111</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -715,22 +709,22 @@
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="K6" s="1">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L6" s="1">
-        <v>5.1970000000000001</v>
+        <v>4.0250000000000004</v>
       </c>
       <c r="M6" s="1">
-        <v>-4.7519999999999998</v>
+        <v>-4.53</v>
       </c>
       <c r="N6" s="1">
-        <v>24.832999999999998</v>
+        <v>20.34</v>
       </c>
       <c r="O6" s="1">
-        <v>955.3</v>
+        <v>903.4</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -741,16 +735,16 @@
         <v>71.62</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1">
-        <v>3.976</v>
+        <v>4.0890000000000004</v>
       </c>
       <c r="F7" s="1">
-        <v>2.4E-2</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -762,22 +756,22 @@
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K7" s="1">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="L7" s="1">
-        <v>4.9619999999999997</v>
+        <v>4.3540000000000001</v>
       </c>
       <c r="M7" s="1">
-        <v>-4.5970000000000004</v>
+        <v>-5.3540000000000001</v>
       </c>
       <c r="N7" s="1">
-        <v>20.192</v>
+        <v>22.806000000000001</v>
       </c>
       <c r="O7" s="1">
-        <v>954.2</v>
+        <v>1045.5</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -788,16 +782,16 @@
         <v>71.62</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1">
-        <v>3.7959999999999998</v>
+        <v>4.1870000000000003</v>
       </c>
       <c r="F8" s="1">
-        <v>3.4000000000000002E-2</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -809,22 +803,22 @@
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="K8" s="1">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L8" s="1">
-        <v>4.0250000000000004</v>
+        <v>4.6289999999999996</v>
       </c>
       <c r="M8" s="1">
-        <v>-4.53</v>
+        <v>-4.931</v>
       </c>
       <c r="N8" s="1">
-        <v>20.34</v>
+        <v>24.196000000000002</v>
       </c>
       <c r="O8" s="1">
-        <v>903.4</v>
+        <v>1287.2</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -835,16 +829,16 @@
         <v>71.62</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1">
-        <v>4.0890000000000004</v>
+        <v>2.6389999999999998</v>
       </c>
       <c r="F9" s="1">
-        <v>5.8999999999999997E-2</v>
+        <v>0.03</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -856,22 +850,22 @@
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K9" s="1">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="L9" s="1">
-        <v>4.3540000000000001</v>
+        <v>4.57</v>
       </c>
       <c r="M9" s="1">
-        <v>-5.3540000000000001</v>
+        <v>-3.6909999999999998</v>
       </c>
       <c r="N9" s="1">
-        <v>22.806000000000001</v>
+        <v>20.861999999999998</v>
       </c>
       <c r="O9" s="1">
-        <v>1045.5</v>
+        <v>506.2</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -885,13 +879,13 @@
         <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1">
-        <v>4.1870000000000003</v>
+        <v>4.5309999999999997</v>
       </c>
       <c r="F10" s="1">
-        <v>4.2999999999999997E-2</v>
+        <v>7.8E-2</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -903,22 +897,22 @@
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K10" s="1">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L10" s="1">
-        <v>4.6289999999999996</v>
+        <v>4.62</v>
       </c>
       <c r="M10" s="1">
-        <v>-4.931</v>
+        <v>-5.0359999999999996</v>
       </c>
       <c r="N10" s="1">
-        <v>24.196000000000002</v>
+        <v>23.53</v>
       </c>
       <c r="O10" s="1">
-        <v>1287.2</v>
+        <v>1226.8</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -932,13 +926,13 @@
         <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E11" s="1">
-        <v>2.6389999999999998</v>
+        <v>4.1660000000000004</v>
       </c>
       <c r="F11" s="1">
-        <v>0.03</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -950,22 +944,22 @@
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="K11" s="1">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="L11" s="1">
-        <v>4.57</v>
+        <v>4.4290000000000003</v>
       </c>
       <c r="M11" s="1">
-        <v>-3.6909999999999998</v>
+        <v>-4.726</v>
       </c>
       <c r="N11" s="1">
-        <v>20.861999999999998</v>
+        <v>25.067</v>
       </c>
       <c r="O11" s="1">
-        <v>506.2</v>
+        <v>1102.2</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -976,16 +970,16 @@
         <v>71.62</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="E12" s="1">
-        <v>4.5309999999999997</v>
+        <v>3.919</v>
       </c>
       <c r="F12" s="1">
-        <v>7.8E-2</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -997,22 +991,22 @@
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K12" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L12" s="1">
-        <v>4.62</v>
+        <v>3.6440000000000001</v>
       </c>
       <c r="M12" s="1">
-        <v>-5.0359999999999996</v>
+        <v>-4.7409999999999997</v>
       </c>
       <c r="N12" s="1">
-        <v>23.53</v>
+        <v>23.766999999999999</v>
       </c>
       <c r="O12" s="1">
-        <v>1226.8</v>
+        <v>825.1</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1023,136 +1017,42 @@
         <v>71.62</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3.887</v>
+      </c>
+      <c r="F13" s="1">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
         <v>35</v>
       </c>
-      <c r="E13" s="1">
-        <v>4.1660000000000004</v>
-      </c>
-      <c r="F13" s="1">
-        <v>8.4000000000000005E-2</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>29</v>
-      </c>
       <c r="K13" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L13" s="1">
-        <v>4.4290000000000003</v>
+        <v>4.2320000000000002</v>
       </c>
       <c r="M13" s="1">
-        <v>-4.726</v>
+        <v>-5.7839999999999998</v>
       </c>
       <c r="N13" s="1">
-        <v>25.067</v>
+        <v>24.041</v>
       </c>
       <c r="O13" s="1">
-        <v>1102.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>46237</v>
-      </c>
-      <c r="B14" s="1">
-        <v>71.62</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="1">
-        <v>3.919</v>
-      </c>
-      <c r="F14" s="1">
-        <v>7.2999999999999995E-2</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>28</v>
-      </c>
-      <c r="K14" s="1">
-        <v>27</v>
-      </c>
-      <c r="L14" s="1">
-        <v>3.6440000000000001</v>
-      </c>
-      <c r="M14" s="1">
-        <v>-4.7409999999999997</v>
-      </c>
-      <c r="N14" s="1">
-        <v>23.766999999999999</v>
-      </c>
-      <c r="O14" s="1">
-        <v>825.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>46237</v>
-      </c>
-      <c r="B15" s="1">
-        <v>71.62</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="1">
-        <v>3.887</v>
-      </c>
-      <c r="F15" s="1">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>35</v>
-      </c>
-      <c r="K15" s="1">
-        <v>17</v>
-      </c>
-      <c r="L15" s="1">
-        <v>4.2320000000000002</v>
-      </c>
-      <c r="M15" s="1">
-        <v>-5.7839999999999998</v>
-      </c>
-      <c r="N15" s="1">
-        <v>24.041</v>
-      </c>
-      <c r="O15" s="1">
         <v>972.5</v>
       </c>
     </row>
